--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R3812a4dc4885464a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Ra7b6409e80534c9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R1df0219790804d1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R0fa5779b336c4701"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R1e85928260b8496c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R8638dd1b2e6c436f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="Rda5d593f2f644463"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="Rbd590052f5c54440"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R385aba81dc294349"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="Rd5e04ff635524176"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Rf079f399ad334304"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R2bf281efbc1f4d8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R84f9394ab5fa4498"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R3be82ce809754bc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="Rd8dace3cf726467b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R37ee086b574d4265"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="Rb9de7cabe322460f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R86e276ebbdc54cec"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2655,7 +2655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1c02425c7763405f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1f4838e3fbad417c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2685,7 +2685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R85b6d07abc184071"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R20005ce613b246d5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2715,7 +2715,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd685d74b5cdc4258"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R452c32a24b724516"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2745,7 +2745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9932d27bef4f408f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdbe802298eff43aa"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2775,7 +2775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0fec2278ac39463c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdaa9566faa684c3e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2810,7 +2810,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbec2c5d1eb024a8e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcc7e62b0c7c343a7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2840,7 +2840,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5535927a18bd425a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc1636bcdabe14730"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2870,7 +2870,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0354150bd16c4667"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0223adf058c54c24"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2900,7 +2900,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2e1d400215d14885"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7fd5e28ab9af4a77"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2930,7 +2930,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7d7731605b9c41bc"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R162cef68c3ec4036"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2965,7 +2965,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R00ee71bb6a294ea1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R10f5695ecadc4ee1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2995,7 +2995,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R50a29c93ec7a4935"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0086ef849ccb4008"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3025,7 +3025,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R71c6ae55c236430f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4944063831634b97"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3055,7 +3055,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9ed78a9b4a8d44d5"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8724986043314702"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4337,7 +4337,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a4b1262333b466d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93c591092b314325"/>
 </x:worksheet>
 </file>
 
@@ -5341,7 +5341,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea3ee92266764a2b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45dce733bb02492a"/>
 </x:worksheet>
 </file>
 
@@ -5349,12 +5349,12 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="54.88999938964844" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="7.440000057220459" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="7.110000133514404" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="54" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="7.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="7" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="14.109999656677246" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14.109999656677246" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
   </x:cols>
@@ -12163,7 +12163,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reebcba79ece4414b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R704a8c1ec9654aa0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12172,19 +12172,19 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="41.560001373291016" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="7.440000057220459" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="7.110000133514404" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="40.779998779296875" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="7.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="7" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="6" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="38" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14.4399995803833" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="11.779999732971191" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="12.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="16.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="9.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="7.110000133514404" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="17.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="22.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="9.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="7" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="17.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="22.219999313354492" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -17202,7 +17202,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R987db0bfe72f496d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref1b0eb5790242d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17211,19 +17211,19 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="41.560001373291016" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="7.440000057220459" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="7.110000133514404" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="40.779998779296875" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="7.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="7" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="6" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="38" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14.4399995803833" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="10.890000343322754" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="11" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="16.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="9.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="7.110000133514404" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="17.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="22.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="10.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="9.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="7" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="17.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="22.219999313354492" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -25181,7 +25181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b73035b34d6401a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e0abda1491849a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25190,16 +25190,16 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="58.439998626708984" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="7.440000057220459" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="7.110000133514404" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="57.33000183105469" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="7.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="7" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="6" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="12.779999732971191" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="12.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="22.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="7.110000133514404" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="7" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -29120,7 +29120,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e6bf0e5ad12484d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf77844028e034de0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29131,16 +29131,16 @@
   <x:cols>
     <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="12.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18.780000686645508" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="17.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16.780000686645508" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="3.7799999713897705" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="5.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="5.329999923706055" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="11.779999732971191" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="11.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="17.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16.780000686645508" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="3.7799999713897705" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="5.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="5.329999923706055" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
@@ -31184,7 +31184,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5427ddb105fe434e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89929c33b5094e18"/>
 </x:worksheet>
 </file>
 
@@ -31192,12 +31192,12 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="40.33000183105469" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="10.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="39.779998779296875" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.220000267028809" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="38" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="15.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15.109999656677246" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -31362,11 +31362,11 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="48.779998779296875" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="47.88999938964844" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="14.109999656677246" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="14.109999656677246" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="3.7799999713897705" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="5.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="5.329999923706055" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="3.7799999713897705" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="34" hidden="0" customWidth="1"/>
   </x:cols>

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="Rd5e04ff635524176"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Rf079f399ad334304"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R2bf281efbc1f4d8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R84f9394ab5fa4498"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R3be82ce809754bc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="Rd8dace3cf726467b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R37ee086b574d4265"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="Rb9de7cabe322460f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R86e276ebbdc54cec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R16138e6473de460e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R2a733b736adc4ec5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R12eb87bd903547eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R1fbf0e878e5341af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R0fab6444e87c4271"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="Rb365c3f1a685474f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R66225f911fe14930"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R0aca273d67c84008"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="Rba771d09b34a4636"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2655,7 +2655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1f4838e3fbad417c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdceb7ba92c4b44ce"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2685,7 +2685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R20005ce613b246d5"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7012f1a137e44154"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2715,7 +2715,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R452c32a24b724516"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6a3047c0187b41d7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2745,7 +2745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdbe802298eff43aa"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R142cbc2fc14c4fee"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2775,7 +2775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdaa9566faa684c3e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc42069a3a1c240ff"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2810,7 +2810,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcc7e62b0c7c343a7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R389e703eab354008"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2840,7 +2840,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc1636bcdabe14730"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra527ac2f838c4670"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2870,7 +2870,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0223adf058c54c24"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R293804e0a7764cc0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2900,7 +2900,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7fd5e28ab9af4a77"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R707b5b00509941a3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2930,7 +2930,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R162cef68c3ec4036"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfc36160afe3a4088"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2965,7 +2965,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R10f5695ecadc4ee1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6575856f92d24bfc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2995,7 +2995,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0086ef849ccb4008"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R185ddf8246c647b6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3025,7 +3025,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4944063831634b97"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb7420a7fa92247a1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3055,7 +3055,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8724986043314702"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2fd513f11c784e86"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4337,7 +4337,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93c591092b314325"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5571e7306dbe449d"/>
 </x:worksheet>
 </file>
 
@@ -5341,7 +5341,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45dce733bb02492a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09f27e5dbd294104"/>
 </x:worksheet>
 </file>
 
@@ -12163,7 +12163,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R704a8c1ec9654aa0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e2875d3d21c4311"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17202,7 +17202,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref1b0eb5790242d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73f2d4b1100141fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25181,7 +25181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e0abda1491849a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc791529f14824678"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29120,7 +29120,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf77844028e034de0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c28f1a5b525474e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31184,7 +31184,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89929c33b5094e18"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f19fd7c376d4aea"/>
 </x:worksheet>
 </file>
 

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R16138e6473de460e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R2a733b736adc4ec5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R12eb87bd903547eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R1fbf0e878e5341af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R0fab6444e87c4271"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="Rb365c3f1a685474f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R66225f911fe14930"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R0aca273d67c84008"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="Rba771d09b34a4636"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R14fb4fd190a44d95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Rf7a5c14cded94769"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R2989047c46eb48d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="Rb811f9a864f34c13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R3752543df82d42c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="Rea06c3deed4e4eaf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R1de17d86989c448e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R71234fe9b5664183"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R5ce31a634e6d4b6f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2655,7 +2655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdceb7ba92c4b44ce"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R30ea9c173a174a3e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2685,7 +2685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7012f1a137e44154"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R99dd7c2de0b04322"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2715,7 +2715,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6a3047c0187b41d7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re83a343a8fe3485d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2745,7 +2745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R142cbc2fc14c4fee"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1d0a867d21234280"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2775,7 +2775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc42069a3a1c240ff"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rca72f7e794bd40ff"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2810,7 +2810,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R389e703eab354008"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R76bd8563badf4f8b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2840,7 +2840,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra527ac2f838c4670"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R14930f66773c4735"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2870,7 +2870,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R293804e0a7764cc0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re85cb0ae8cd44d2d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2900,7 +2900,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R707b5b00509941a3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R42900267406344f0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2930,7 +2930,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfc36160afe3a4088"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R79c22dae4bba4dcb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2965,7 +2965,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6575856f92d24bfc"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4e6558c695b34eb5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2995,7 +2995,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R185ddf8246c647b6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rae1dbf6996f14af1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3025,7 +3025,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb7420a7fa92247a1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc01c6d2fbb2e4954"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3055,7 +3055,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2fd513f11c784e86"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfdf4a418b2a140bd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4337,7 +4337,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5571e7306dbe449d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re88c3bd6649e4c5e"/>
 </x:worksheet>
 </file>
 
@@ -5341,7 +5341,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09f27e5dbd294104"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf385491f3b864d56"/>
 </x:worksheet>
 </file>
 
@@ -12163,7 +12163,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e2875d3d21c4311"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3f298054a894a01"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17202,7 +17202,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73f2d4b1100141fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ef8620cc5d840f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25181,7 +25181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc791529f14824678"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R899b3b56696a49ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29120,7 +29120,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c28f1a5b525474e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cba78c2fc1d48bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31184,7 +31184,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f19fd7c376d4aea"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec065519288a47f0"/>
 </x:worksheet>
 </file>
 

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R14fb4fd190a44d95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Rf7a5c14cded94769"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R2989047c46eb48d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="Rb811f9a864f34c13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R3752543df82d42c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="Rea06c3deed4e4eaf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R1de17d86989c448e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R71234fe9b5664183"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R5ce31a634e6d4b6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R85f7e15456d14a35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R4779a19af6f84f5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R78f6caddb46b410f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R652a608252064bf8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R495d87e31d5443e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="Rec16e0016c9c492f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R57b2332b43e04b0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R75ea4be4fb5440bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="Ra78fdc976cd94c80"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2655,7 +2655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R30ea9c173a174a3e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3e5b30a0ec714529"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2685,7 +2685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R99dd7c2de0b04322"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re440addf0fb049ad"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2715,7 +2715,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re83a343a8fe3485d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9dcf587a2b274191"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2745,7 +2745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1d0a867d21234280"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R90d7ddaf7d9546ca"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2775,7 +2775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rca72f7e794bd40ff"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R53f13fefe14e49a1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2810,7 +2810,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R76bd8563badf4f8b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3de306e122414e7f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2840,7 +2840,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R14930f66773c4735"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7b6b8a2362b14d88"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2870,7 +2870,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re85cb0ae8cd44d2d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4dae95e53834404c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2900,7 +2900,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R42900267406344f0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R88b595d6deaa41e0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2930,7 +2930,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R79c22dae4bba4dcb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf687e2bbf59f43e2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2965,7 +2965,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4e6558c695b34eb5"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra745a410504a4a8a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2995,7 +2995,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rae1dbf6996f14af1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8b3930000f944d1d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3025,7 +3025,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc01c6d2fbb2e4954"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd27d0e074da04c2d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3055,7 +3055,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfdf4a418b2a140bd"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf933de58d70b41d5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4337,7 +4337,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re88c3bd6649e4c5e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc396926ea29e4546"/>
 </x:worksheet>
 </file>
 
@@ -5341,7 +5341,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf385491f3b864d56"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref9549a0c7f440f5"/>
 </x:worksheet>
 </file>
 
@@ -12163,7 +12163,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3f298054a894a01"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4d3980aca9f4408"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17202,7 +17202,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ef8620cc5d840f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20fe32f175264193"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25181,7 +25181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R899b3b56696a49ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bce21caa9a147a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29120,7 +29120,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cba78c2fc1d48bc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re306254dae3c4d2d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31184,7 +31184,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec065519288a47f0"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d8c3a6408a140bc"/>
 </x:worksheet>
 </file>
 

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R85f7e15456d14a35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R4779a19af6f84f5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R78f6caddb46b410f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R652a608252064bf8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R495d87e31d5443e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="Rec16e0016c9c492f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R57b2332b43e04b0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R75ea4be4fb5440bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="Ra78fdc976cd94c80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R0189154c3f3645fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R800ab0c7a5344239"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="Rd2d7a155021349ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="Reeb6806096b841a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R1c5f179b58554809"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R6c0ae04ef0194448"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R6806ecb003b244e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="Rd2a6abe838cf4346"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R059f0dc7dede4c77"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2655,7 +2655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3e5b30a0ec714529"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd6731da404f2482b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2685,7 +2685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re440addf0fb049ad"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb532c68620754d29"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2715,7 +2715,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9dcf587a2b274191"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3f8eba250d8e4e3d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2745,7 +2745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R90d7ddaf7d9546ca"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8740102aeadf4191"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2775,7 +2775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R53f13fefe14e49a1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rde7658bffc6640ca"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2810,7 +2810,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3de306e122414e7f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5246295eab0d4ada"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2840,7 +2840,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7b6b8a2362b14d88"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7936581d05e94d50"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2870,7 +2870,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4dae95e53834404c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3bfd37c8aaaa42fd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2900,7 +2900,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R88b595d6deaa41e0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdef1920f5dd04061"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2930,7 +2930,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf687e2bbf59f43e2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R068855011ba24b8e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2965,7 +2965,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra745a410504a4a8a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcaa3ee16ee8444b9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2995,7 +2995,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8b3930000f944d1d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R22b07c69b4d644d4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3025,7 +3025,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd27d0e074da04c2d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0852651fbbaf4936"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3055,7 +3055,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf933de58d70b41d5"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R291e3a92fe774bf3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4337,7 +4337,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc396926ea29e4546"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ae98b5b7ab84d80"/>
 </x:worksheet>
 </file>
 
@@ -5341,7 +5341,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref9549a0c7f440f5"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra073f4a919044c62"/>
 </x:worksheet>
 </file>
 
@@ -12163,7 +12163,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4d3980aca9f4408"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65feda3639bd43d7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17202,7 +17202,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20fe32f175264193"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re95d6e070e5b4f72"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25181,7 +25181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bce21caa9a147a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50e00cd02cab488c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29120,7 +29120,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re306254dae3c4d2d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10e4eba110fe483b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31184,7 +31184,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d8c3a6408a140bc"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbea229a22f14f00"/>
 </x:worksheet>
 </file>
 

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R0189154c3f3645fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R800ab0c7a5344239"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="Rd2d7a155021349ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="Reeb6806096b841a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R1c5f179b58554809"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R6c0ae04ef0194448"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R6806ecb003b244e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="Rd2a6abe838cf4346"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R059f0dc7dede4c77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R65720f55b5bb476f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Re30526bcfafc4cdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R6422e25476744a6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R01343b876c3e4b12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R75286f0a430b48fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R42bf44f2dd214016"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="Rf2dc764501e94f2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="Ra35521e67ffa4197"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R3c607e0c51004df1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2655,7 +2655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd6731da404f2482b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R054b724c9154460a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2685,7 +2685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb532c68620754d29"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R158c0180f6ae45cb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2715,7 +2715,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3f8eba250d8e4e3d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb4fbbdc47ede4e98"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2745,7 +2745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8740102aeadf4191"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rde9c4a600fdf409a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2775,7 +2775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rde7658bffc6640ca"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6188a9fb15dd410e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2810,7 +2810,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5246295eab0d4ada"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R18aa5f4238f74e45"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2840,7 +2840,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7936581d05e94d50"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd69a248e68c74c01"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2870,7 +2870,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3bfd37c8aaaa42fd"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5ed86e91a4b44284"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2900,7 +2900,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdef1920f5dd04061"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3b3f723b089a4ba0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2930,7 +2930,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R068855011ba24b8e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3c262c474ebf4e63"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2965,7 +2965,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcaa3ee16ee8444b9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R99628a05802c464f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2995,7 +2995,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R22b07c69b4d644d4"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd83d691d502f4dd7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3025,7 +3025,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0852651fbbaf4936"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd4a977c36d6f42ef"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3055,7 +3055,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R291e3a92fe774bf3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb9e58bea53e14ca1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4337,7 +4337,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ae98b5b7ab84d80"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54f0cd77f22949f4"/>
 </x:worksheet>
 </file>
 
@@ -5341,7 +5341,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra073f4a919044c62"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re97bcbc857464083"/>
 </x:worksheet>
 </file>
 
@@ -12163,7 +12163,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65feda3639bd43d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02a98be7da7d45f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17202,7 +17202,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re95d6e070e5b4f72"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac616228895f4e14"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25181,7 +25181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50e00cd02cab488c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88a74f716c294e16"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29120,7 +29120,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10e4eba110fe483b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78051da5412e4ade"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31184,7 +31184,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbea229a22f14f00"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5ba9b2823a44c7a"/>
 </x:worksheet>
 </file>
 

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R65720f55b5bb476f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Re30526bcfafc4cdb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R6422e25476744a6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R01343b876c3e4b12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R75286f0a430b48fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R42bf44f2dd214016"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="Rf2dc764501e94f2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="Ra35521e67ffa4197"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R3c607e0c51004df1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="Rd7931cd9f8db414a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Rb7c9a26de5664528"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="Re2094d04b8f14e0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="Raab60a3acc3a456b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="Rb447336156bd4082"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R62092ec6f6424b05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R9ef460a6cb184dc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R01c9137f108740d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R58d7dfd1ad8b4e94"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2655,7 +2655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R054b724c9154460a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd22a399ffb8a4d31"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2685,7 +2685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R158c0180f6ae45cb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdb816f6db024427c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2715,7 +2715,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb4fbbdc47ede4e98"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf8786d11a6b74f82"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2745,7 +2745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rde9c4a600fdf409a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2aa79cac6afd45df"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2775,7 +2775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6188a9fb15dd410e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rae49551f0a924ab7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2810,7 +2810,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R18aa5f4238f74e45"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra68277b2e3fa4f2c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2840,7 +2840,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd69a248e68c74c01"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R95a3209653d248ed"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2870,7 +2870,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5ed86e91a4b44284"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R68da3f74b4a14edf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2900,7 +2900,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3b3f723b089a4ba0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R988b5921d11d4a2a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2930,7 +2930,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3c262c474ebf4e63"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R65708977efe74a89"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2965,7 +2965,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R99628a05802c464f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra8fe827c687b4226"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2995,7 +2995,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd83d691d502f4dd7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re3d77e4730244343"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3025,7 +3025,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd4a977c36d6f42ef"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R358716d0cf0347ed"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3055,7 +3055,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb9e58bea53e14ca1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R54b5ddd37d144588"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4337,7 +4337,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54f0cd77f22949f4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb01f86bab3b44494"/>
 </x:worksheet>
 </file>
 
@@ -5341,7 +5341,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re97bcbc857464083"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0afbd858b00141ce"/>
 </x:worksheet>
 </file>
 
@@ -12163,7 +12163,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02a98be7da7d45f2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94cac6a230e3422c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17202,7 +17202,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac616228895f4e14"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89e24632dfd8428c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25181,7 +25181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88a74f716c294e16"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdbe2e9fc03c44bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29120,7 +29120,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78051da5412e4ade"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fa78ccedd7349a8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31184,7 +31184,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5ba9b2823a44c7a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c9957f2ccc242d1"/>
 </x:worksheet>
 </file>
 

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="Rd7931cd9f8db414a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Rb7c9a26de5664528"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="Re2094d04b8f14e0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="Raab60a3acc3a456b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="Rb447336156bd4082"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R62092ec6f6424b05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R9ef460a6cb184dc5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R01c9137f108740d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R58d7dfd1ad8b4e94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R468ff5bce0244b33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Ra71b57f415764286"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R6596ab2bb931494e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="Rf5f9aee13c314282"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="Reefb2ad7af984cb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R951852dfa3784fae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R04e711c17872477e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="Rcaa685307b1f4959"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R72f7dadc25f34d44"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2655,7 +2655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd22a399ffb8a4d31"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R21cd07fe01494e04"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2685,7 +2685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdb816f6db024427c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R87d3aef8933c4776"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2715,7 +2715,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf8786d11a6b74f82"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R193f6046398e41d8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2745,7 +2745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2aa79cac6afd45df"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6fd71925e68d4104"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2775,7 +2775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rae49551f0a924ab7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R093f0115dc294a2c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2810,7 +2810,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra68277b2e3fa4f2c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ref006b53a93b4642"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2840,7 +2840,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R95a3209653d248ed"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb48316bca3a44e97"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2870,7 +2870,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R68da3f74b4a14edf"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra6f0342097ff49f1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2900,7 +2900,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R988b5921d11d4a2a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1d890c14c7104622"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2930,7 +2930,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R65708977efe74a89"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2166faa2226e4e7d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2965,7 +2965,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra8fe827c687b4226"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra32ec1fe4434401a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2995,7 +2995,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re3d77e4730244343"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0769e865610b45cc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3025,7 +3025,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R358716d0cf0347ed"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R89ce5086ce694913"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3055,7 +3055,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R54b5ddd37d144588"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcc01a7f871794dd3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4337,7 +4337,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb01f86bab3b44494"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd03d1cdccdba45a6"/>
 </x:worksheet>
 </file>
 
@@ -5341,7 +5341,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0afbd858b00141ce"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c79636cc3354ccd"/>
 </x:worksheet>
 </file>
 
@@ -12163,7 +12163,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94cac6a230e3422c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R156109c5f58e4c0a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17202,7 +17202,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89e24632dfd8428c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R807e4b9a9c2d4018"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25181,7 +25181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdbe2e9fc03c44bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4ca048d88954d7d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29120,7 +29120,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fa78ccedd7349a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d4822f024634e01"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31184,7 +31184,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c9957f2ccc242d1"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d08b5e634cd4c7c"/>
 </x:worksheet>
 </file>
 

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R468ff5bce0244b33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Ra71b57f415764286"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R6596ab2bb931494e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="Rf5f9aee13c314282"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="Reefb2ad7af984cb5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R951852dfa3784fae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R04e711c17872477e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="Rcaa685307b1f4959"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R72f7dadc25f34d44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="Rd975c466941543b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R6603afb56a0a40a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="Rec98a7cf62df4267"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="Rbb2fc4c1a38e4fc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="Re0fb3ce194ea4496"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R65177d3c74584d35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R29e5910c8ef948f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="Raf7bc20b37fc4149"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R575eff717cc94458"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2655,7 +2655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R21cd07fe01494e04"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re6f8d14e33d84cd8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2685,7 +2685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R87d3aef8933c4776"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rba68cc26e3a74384"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2715,7 +2715,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R193f6046398e41d8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd4e65c924ea1403b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2745,7 +2745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6fd71925e68d4104"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfbc0ff2a7581403d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2775,7 +2775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R093f0115dc294a2c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9dc8991cb2fc41d0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2810,7 +2810,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ref006b53a93b4642"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Reb4d53daef9941bd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2840,7 +2840,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb48316bca3a44e97"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcc493e1aa6f94654"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2870,7 +2870,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra6f0342097ff49f1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra07566a240d34f49"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2900,7 +2900,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1d890c14c7104622"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3e21f4b36bc94ead"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2930,7 +2930,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2166faa2226e4e7d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R419ac2b2afbd45c2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2965,7 +2965,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra32ec1fe4434401a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7b222d3aa5254962"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2995,7 +2995,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0769e865610b45cc"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R74ad9473dd564159"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3025,7 +3025,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R89ce5086ce694913"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R91e70575c642471b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3055,7 +3055,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcc01a7f871794dd3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R825e41c996494f13"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4337,7 +4337,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd03d1cdccdba45a6"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4180edb6fc7b4351"/>
 </x:worksheet>
 </file>
 
@@ -5341,7 +5341,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c79636cc3354ccd"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd129e95fc2764057"/>
 </x:worksheet>
 </file>
 
@@ -12163,7 +12163,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R156109c5f58e4c0a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra99ae876aad54389"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17202,7 +17202,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R807e4b9a9c2d4018"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ea11315484c482d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25181,7 +25181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4ca048d88954d7d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c7ad4172d024b84"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29120,7 +29120,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d4822f024634e01"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ad091ff2bac41f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31184,7 +31184,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d08b5e634cd4c7c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d1a937685cf4d8a"/>
 </x:worksheet>
 </file>
 

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="Rd975c466941543b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R6603afb56a0a40a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="Rec98a7cf62df4267"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="Rbb2fc4c1a38e4fc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="Re0fb3ce194ea4496"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R65177d3c74584d35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R29e5910c8ef948f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="Raf7bc20b37fc4149"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R575eff717cc94458"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R79fd0ae515194258"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R91d35fd9e83a4083"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="Raa21e10163244871"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="Re05ce098ac6b43b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R50e1463c4c16497d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R8ef4d2d4225b4cdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R8d0a9c1d0d064dcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R2cd62c83a4e74683"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R6ec812970f064b55"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2655,7 +2655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re6f8d14e33d84cd8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R75c06e297012420d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2685,7 +2685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rba68cc26e3a74384"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R14e0e9b9b8e14fc6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2715,7 +2715,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd4e65c924ea1403b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra998326a16ce4eee"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2745,7 +2745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfbc0ff2a7581403d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbc0f60ebea6f4669"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2775,7 +2775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9dc8991cb2fc41d0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0befaa4938ce4e88"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2810,7 +2810,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Reb4d53daef9941bd"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3230188e49394042"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2840,7 +2840,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcc493e1aa6f94654"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R74347fd7f62f4587"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2870,7 +2870,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra07566a240d34f49"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb9572a3eb2944462"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2900,7 +2900,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3e21f4b36bc94ead"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5dfc0e927d8b4f50"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2930,7 +2930,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R419ac2b2afbd45c2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf2b7e2d241b44d56"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2965,7 +2965,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7b222d3aa5254962"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R69187622d1ed44c4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2995,7 +2995,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R74ad9473dd564159"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R47cfc51e108d49a5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3025,7 +3025,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R91e70575c642471b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re63e45e77b494db5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3055,7 +3055,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R825e41c996494f13"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R699d3bc09ecd4df1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4337,7 +4337,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4180edb6fc7b4351"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74d8411ac72a4494"/>
 </x:worksheet>
 </file>
 
@@ -5341,7 +5341,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd129e95fc2764057"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a2e2c3d29644de3"/>
 </x:worksheet>
 </file>
 
@@ -12163,7 +12163,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra99ae876aad54389"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf1ea61bd94a4e84"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17202,7 +17202,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ea11315484c482d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf334d0ad80094575"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25181,7 +25181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c7ad4172d024b84"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5be6d935c8924893"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29120,7 +29120,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ad091ff2bac41f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R678da7445d2d4b74"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31184,7 +31184,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d1a937685cf4d8a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48597505aed247f6"/>
 </x:worksheet>
 </file>
 

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R79fd0ae515194258"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R91d35fd9e83a4083"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="Raa21e10163244871"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="Re05ce098ac6b43b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R50e1463c4c16497d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R8ef4d2d4225b4cdb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R8d0a9c1d0d064dcc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R2cd62c83a4e74683"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R6ec812970f064b55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="Reb80ec882c40477d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Rd616d45f0a3f4f32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R3040730fc5004103"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="Raef9cbd489ba4da3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R91e5ab4277cf4c5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="Rc1cc445724af4077"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R25633b4418f04d58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R4dacc54a17ae4136"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="Reb6b693138734043"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2655,7 +2655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R75c06e297012420d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra4c147eb57a746ec"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2685,7 +2685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R14e0e9b9b8e14fc6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb45578aa604541ed"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2715,7 +2715,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra998326a16ce4eee"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R50610a2ad42a452f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2745,7 +2745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbc0f60ebea6f4669"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R14555a2526964adf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2775,7 +2775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0befaa4938ce4e88"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R01ad3bc2c03e4049"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2810,7 +2810,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3230188e49394042"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3573e2f1a8c74cbd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2840,7 +2840,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R74347fd7f62f4587"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9ecc2f7c37ec466a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2870,7 +2870,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb9572a3eb2944462"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5e5fb5aa0cca456a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2900,7 +2900,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5dfc0e927d8b4f50"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8b52b8f116b1428d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2930,7 +2930,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf2b7e2d241b44d56"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb4e077c1a1a74fb8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2965,7 +2965,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R69187622d1ed44c4"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R733d041543dc4ae0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2995,7 +2995,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R47cfc51e108d49a5"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R74a16053682a41c7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3025,7 +3025,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re63e45e77b494db5"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rad6679e69bcf420d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3055,7 +3055,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R699d3bc09ecd4df1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R778bd3a44e12415f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4337,7 +4337,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74d8411ac72a4494"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91e19b67e47f4da4"/>
 </x:worksheet>
 </file>
 
@@ -5341,7 +5341,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a2e2c3d29644de3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R403773144b114bdd"/>
 </x:worksheet>
 </file>
 
@@ -12163,7 +12163,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf1ea61bd94a4e84"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4803184d5cb745e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17202,7 +17202,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf334d0ad80094575"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66c8c1cea7714e04"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25181,7 +25181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5be6d935c8924893"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43d565160dac4f6a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29120,7 +29120,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R678da7445d2d4b74"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R307dc04a886f453f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31184,7 +31184,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48597505aed247f6"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3030844518f84bf4"/>
 </x:worksheet>
 </file>
 

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="Reb80ec882c40477d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Rd616d45f0a3f4f32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R3040730fc5004103"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="Raef9cbd489ba4da3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R91e5ab4277cf4c5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="Rc1cc445724af4077"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R25633b4418f04d58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R4dacc54a17ae4136"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="Reb6b693138734043"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="Rb8c25c88a2f640c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Rfbf4731fed154582"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="Re3083570204b47dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R3cd99703685841da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R3a6dccb0afb5447f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="Ra7ef2fe6150e47a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="Red8fc15f34ff41ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="Rcc903e8c231247d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R404a20a288e44e85"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2655,7 +2655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra4c147eb57a746ec"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3e090fc872ca44d6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2685,7 +2685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb45578aa604541ed"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Raa4e2ceca7f24e18"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2715,7 +2715,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R50610a2ad42a452f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R86de0416bd58434f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2745,7 +2745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R14555a2526964adf"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R56aa6737fda142aa"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2775,7 +2775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R01ad3bc2c03e4049"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb5dc42da74c84112"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2810,7 +2810,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3573e2f1a8c74cbd"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf3830c8402c244e3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2840,7 +2840,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9ecc2f7c37ec466a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc9594640f7114fed"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2870,7 +2870,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5e5fb5aa0cca456a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf81d2728f128444b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2900,7 +2900,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8b52b8f116b1428d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rab58cca5d14e4623"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2930,7 +2930,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb4e077c1a1a74fb8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8625e1dcd2294341"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2965,7 +2965,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R733d041543dc4ae0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R76d4b215d0584385"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2995,7 +2995,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R74a16053682a41c7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rff0db4a54fc84930"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3025,7 +3025,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rad6679e69bcf420d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd1c86133f7e64f98"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3055,7 +3055,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R778bd3a44e12415f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2c2bd3ae2f164974"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4337,7 +4337,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91e19b67e47f4da4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33d1fef28b724a17"/>
 </x:worksheet>
 </file>
 
@@ -5341,7 +5341,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R403773144b114bdd"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcf6dd24f2d64d51"/>
 </x:worksheet>
 </file>
 
@@ -12163,7 +12163,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4803184d5cb745e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R710eded6acdf4e5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17202,7 +17202,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66c8c1cea7714e04"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fefa60842ba4dd8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25181,7 +25181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43d565160dac4f6a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re180f79d5ec64f01"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29120,7 +29120,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R307dc04a886f453f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85f230f5829c4526"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31184,7 +31184,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3030844518f84bf4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf83ae911498749b3"/>
 </x:worksheet>
 </file>
 

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="Rb8c25c88a2f640c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Rfbf4731fed154582"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="Re3083570204b47dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R3cd99703685841da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R3a6dccb0afb5447f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="Ra7ef2fe6150e47a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="Red8fc15f34ff41ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="Rcc903e8c231247d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R404a20a288e44e85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R825cc193f0cd4aa9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R853fbe0f966e49fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R494c99e4f2544cc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="Rb8947f625ae0499a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R15fdb9e66c8a43ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="Rac8b963716a84e45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R4ab0298c37e7431f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R0322e687f93c4ad1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R667d9e4fbeed4f6b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2655,7 +2655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3e090fc872ca44d6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf44f6562f17a42a6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2685,7 +2685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Raa4e2ceca7f24e18"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1caf2b0c6800464f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2715,7 +2715,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R86de0416bd58434f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R15dd3ec88e6744fd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2745,7 +2745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R56aa6737fda142aa"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R86e3a322b43345f6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2775,7 +2775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb5dc42da74c84112"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rff712bddecc64497"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2810,7 +2810,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf3830c8402c244e3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rea924895a4264d52"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2840,7 +2840,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc9594640f7114fed"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R09e32470167c4f9a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2870,7 +2870,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf81d2728f128444b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2f171b1dfc4c4173"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2900,7 +2900,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rab58cca5d14e4623"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra097d7657f3343fa"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2930,7 +2930,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8625e1dcd2294341"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7e122b94fc6e4ca5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2965,7 +2965,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R76d4b215d0584385"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R93102fb084544f74"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2995,7 +2995,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rff0db4a54fc84930"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7c36e7838f7b4924"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3025,7 +3025,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd1c86133f7e64f98"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1f80c35b77c84887"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3055,7 +3055,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2c2bd3ae2f164974"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1f97fe29f7854439"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4337,7 +4337,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33d1fef28b724a17"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8ecd77faad94367"/>
 </x:worksheet>
 </file>
 
@@ -5341,7 +5341,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcf6dd24f2d64d51"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R657b1a641b514182"/>
 </x:worksheet>
 </file>
 
@@ -12163,7 +12163,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R710eded6acdf4e5c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98114d01c28f4268"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17202,7 +17202,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fefa60842ba4dd8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63ec28a41f044c18"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25181,7 +25181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re180f79d5ec64f01"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e95a6abd8804d74"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29120,7 +29120,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85f230f5829c4526"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b35972f3dfd44cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31184,7 +31184,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf83ae911498749b3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R460a8b402be441fd"/>
 </x:worksheet>
 </file>
 

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R825cc193f0cd4aa9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R853fbe0f966e49fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R494c99e4f2544cc5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="Rb8947f625ae0499a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R15fdb9e66c8a43ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="Rac8b963716a84e45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R4ab0298c37e7431f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R0322e687f93c4ad1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R667d9e4fbeed4f6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R1c57d10b3b264702"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R9a4f9ba022d2448e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R858da425eedb4844"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R7d88857b7a504275"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R86666a0b4495464a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="Rdcc78c6b5c2649bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R6ac14f728e2c4d97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R2c1dcfdc2afd44bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R165ed6f306d741be"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2655,7 +2655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf44f6562f17a42a6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbd9e356a54fb4b43"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2685,7 +2685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1caf2b0c6800464f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R25dd8044ca4f40d4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2715,7 +2715,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R15dd3ec88e6744fd"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2bb194bb67564b58"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2745,7 +2745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R86e3a322b43345f6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3380a130ed754b79"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2775,7 +2775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rff712bddecc64497"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R32923bc6bcd546ca"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2810,7 +2810,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rea924895a4264d52"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R198f0ffcea2d418f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2840,7 +2840,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R09e32470167c4f9a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0c8a0309fc504c14"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2870,7 +2870,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2f171b1dfc4c4173"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9f9c0fe86f6c478a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2900,7 +2900,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra097d7657f3343fa"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0013f9bac38b42b3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2930,7 +2930,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7e122b94fc6e4ca5"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2d9483e506114b7a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2965,7 +2965,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R93102fb084544f74"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rce68794450d84f11"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2995,7 +2995,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7c36e7838f7b4924"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0fde23d1471e4738"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3025,7 +3025,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1f80c35b77c84887"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6b3b663ed8604080"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3055,7 +3055,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1f97fe29f7854439"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3970b1f3b5424298"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4337,7 +4337,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8ecd77faad94367"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac7293bce489445b"/>
 </x:worksheet>
 </file>
 
@@ -5341,7 +5341,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R657b1a641b514182"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7fe3fcab00e4011"/>
 </x:worksheet>
 </file>
 
@@ -12163,7 +12163,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98114d01c28f4268"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42db72e92f6d4940"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17202,7 +17202,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63ec28a41f044c18"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4bd41cc8e414605"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25181,7 +25181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e95a6abd8804d74"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R948a367fdd2a4d50"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29120,7 +29120,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b35972f3dfd44cb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7719e9b08e74c2d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31184,7 +31184,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R460a8b402be441fd"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1d9cebd3e6a41f4"/>
 </x:worksheet>
 </file>
 

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R1c57d10b3b264702"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R9a4f9ba022d2448e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R858da425eedb4844"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R7d88857b7a504275"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R86666a0b4495464a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="Rdcc78c6b5c2649bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R6ac14f728e2c4d97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R2c1dcfdc2afd44bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R165ed6f306d741be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R6a59abc6c4a544df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R4926386e0fa74126"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R4153188b7cd94827"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="Rb5bcc414c0f54b1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="Rf9a36b73ad414b8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R6db82cdc2b3b4c91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="Rdd37b9b7b40d47b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R247f6ba517294538"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R32439c4c69804529"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2655,7 +2655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbd9e356a54fb4b43"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7370f3751e3a4f6a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2685,7 +2685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R25dd8044ca4f40d4"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R794b6d51f1844b8e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2715,7 +2715,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2bb194bb67564b58"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7a7a9115c261418a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2745,7 +2745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3380a130ed754b79"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re12fca8cdf1e4884"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2775,7 +2775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R32923bc6bcd546ca"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1144f75b39cf472b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2810,7 +2810,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R198f0ffcea2d418f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R549e92d8b1b24782"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2840,7 +2840,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0c8a0309fc504c14"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfa507ee08b554b1b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2870,7 +2870,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9f9c0fe86f6c478a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2fbbfde0630545db"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2900,7 +2900,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0013f9bac38b42b3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2a55ef5c04c74e2b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2930,7 +2930,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2d9483e506114b7a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re012df531dcc4fc5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2965,7 +2965,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rce68794450d84f11"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R368d721bb6d449ce"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2995,7 +2995,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0fde23d1471e4738"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc9b7e94a4cb4426e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3025,7 +3025,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6b3b663ed8604080"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb4affada409b4db7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3055,7 +3055,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3970b1f3b5424298"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R22fab49cbd594d20"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4337,7 +4337,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac7293bce489445b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R659116616f0f470a"/>
 </x:worksheet>
 </file>
 
@@ -5341,7 +5341,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7fe3fcab00e4011"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra23fdbd4043a4c85"/>
 </x:worksheet>
 </file>
 
@@ -12163,7 +12163,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42db72e92f6d4940"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15dae7c367c24243"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17202,7 +17202,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4bd41cc8e414605"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7a45f3e7b3b4bab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25181,7 +25181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R948a367fdd2a4d50"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf08206d9fd234f07"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29120,7 +29120,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7719e9b08e74c2d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5f576cdb2104572"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31184,7 +31184,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1d9cebd3e6a41f4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0fa5f178aa6b43d2"/>
 </x:worksheet>
 </file>
 

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R6a59abc6c4a544df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R4926386e0fa74126"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R4153188b7cd94827"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="Rb5bcc414c0f54b1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="Rf9a36b73ad414b8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R6db82cdc2b3b4c91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="Rdd37b9b7b40d47b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R247f6ba517294538"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R32439c4c69804529"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R6dfd51657e554b87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Rb509c8dfb73e4782"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="Rf167a7a90d714bb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R7d7086f001884629"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R342dd6c011b54ab6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="Reeef3147f8584726"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="Re25381cf6cd44a6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R574aaeb773034ed7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R670c75a40b284825"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2655,7 +2655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7370f3751e3a4f6a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra3182abc15e14bcd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2685,7 +2685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R794b6d51f1844b8e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R673642e95e9743cb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2715,7 +2715,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7a7a9115c261418a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6a2dbc41461d483b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2745,7 +2745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re12fca8cdf1e4884"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R456bcd511b8a4091"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2775,7 +2775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1144f75b39cf472b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1a10795e41bb41b5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2810,7 +2810,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R549e92d8b1b24782"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rce4c3604829b4534"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2840,7 +2840,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfa507ee08b554b1b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R51f33e17674c4686"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2870,7 +2870,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2fbbfde0630545db"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb982d86ba55c41c3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2900,7 +2900,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2a55ef5c04c74e2b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra01d16b1a8124a6f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2930,7 +2930,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re012df531dcc4fc5"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2754e3028f024d2e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2965,7 +2965,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R368d721bb6d449ce"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7d54b2fd9e564654"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2995,7 +2995,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc9b7e94a4cb4426e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1e911c15f1094dc2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3025,7 +3025,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb4affada409b4db7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra2e405dcf1e34232"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3055,7 +3055,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R22fab49cbd594d20"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rca2d3f3391784cdd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4337,7 +4337,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R659116616f0f470a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd942f8e932784359"/>
 </x:worksheet>
 </file>
 
@@ -5341,7 +5341,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra23fdbd4043a4c85"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99ea996d5e3643d0"/>
 </x:worksheet>
 </file>
 
@@ -12163,7 +12163,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15dae7c367c24243"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f8e9c3c47bd4e85"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17202,7 +17202,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7a45f3e7b3b4bab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc6e9ed939ba4387"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25181,7 +25181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf08206d9fd234f07"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a59841ce48e41f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29120,7 +29120,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5f576cdb2104572"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9aa5a0f5e1e04ceb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31184,7 +31184,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0fa5f178aa6b43d2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d22b3bc8a764117"/>
 </x:worksheet>
 </file>
 

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R6dfd51657e554b87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Rb509c8dfb73e4782"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="Rf167a7a90d714bb7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R7d7086f001884629"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R342dd6c011b54ab6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="Reeef3147f8584726"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="Re25381cf6cd44a6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R574aaeb773034ed7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R670c75a40b284825"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="Rd5073170927644a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R31d59d2873124d75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R1ebce5ae479b4e53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R371c7f7e04194892"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R101ff6e007004cb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R36d1f7ab2a7c465c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="Rf8dc3a17d37a4c9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R65f683e02c3b4a66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R119c716a548641fc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2655,7 +2655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra3182abc15e14bcd"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rff6639007067431b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2685,7 +2685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R673642e95e9743cb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R04b70f32b0d54c34"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2715,7 +2715,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6a2dbc41461d483b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3ee04dbc4955402d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2745,7 +2745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R456bcd511b8a4091"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7311094e36484844"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2775,7 +2775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1a10795e41bb41b5"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8c7c993438f24c83"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2810,7 +2810,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rce4c3604829b4534"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3ddff776800b4d56"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2840,7 +2840,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R51f33e17674c4686"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbde03374d9d74926"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2870,7 +2870,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb982d86ba55c41c3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R86569570fcaf493c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2900,7 +2900,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra01d16b1a8124a6f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3c018f1bec034358"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2930,7 +2930,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2754e3028f024d2e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2ac6523dbfb24c3a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2965,7 +2965,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7d54b2fd9e564654"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R729e335f31c44b3b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2995,7 +2995,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1e911c15f1094dc2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1105a105d9f1406c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3025,7 +3025,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra2e405dcf1e34232"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rea438f874be84daf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3055,7 +3055,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rca2d3f3391784cdd"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R98297b63f66f4a97"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4337,7 +4337,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd942f8e932784359"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R585930cb489a45a4"/>
 </x:worksheet>
 </file>
 
@@ -5341,7 +5341,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99ea996d5e3643d0"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf93e3c0e9944c5e"/>
 </x:worksheet>
 </file>
 
@@ -12163,7 +12163,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f8e9c3c47bd4e85"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R219cbe2d8f074248"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17202,7 +17202,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc6e9ed939ba4387"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbeb6791ce11a4eb0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25181,7 +25181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a59841ce48e41f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f36abef9ab44202"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29120,7 +29120,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9aa5a0f5e1e04ceb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d6d65184d69425f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31184,7 +31184,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d22b3bc8a764117"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27698423ee544fa2"/>
 </x:worksheet>
 </file>
 

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="Rd5073170927644a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R31d59d2873124d75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R1ebce5ae479b4e53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R371c7f7e04194892"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R101ff6e007004cb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R36d1f7ab2a7c465c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="Rf8dc3a17d37a4c9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R65f683e02c3b4a66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R119c716a548641fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R950f6761ae704841"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R345e5f0e61084bee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="Ra4a3b3e512034d32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="Rff62299695b241be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R0b8d0cf173cf43ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R986389157e7242ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="Rbf1017ec67fa4b32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="Rbf9114ab56eb41d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="Rb273398bdfd84224"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2655,7 +2655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rff6639007067431b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Refdc03b54b804de1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2685,7 +2685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R04b70f32b0d54c34"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb231b35f5cc84572"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2715,7 +2715,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3ee04dbc4955402d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2c838a5f643242b8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2745,7 +2745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7311094e36484844"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd057cddf94f946fd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2775,7 +2775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8c7c993438f24c83"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9e785be6c521411e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2810,7 +2810,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3ddff776800b4d56"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6bd670ec7e384bf6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2840,7 +2840,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbde03374d9d74926"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc6cf4fe7e4d94e50"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2870,7 +2870,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R86569570fcaf493c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8f54e50fad3e4024"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2900,7 +2900,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3c018f1bec034358"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb915fe3e6d954c76"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2930,7 +2930,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2ac6523dbfb24c3a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re0b258ff64c2403c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2965,7 +2965,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R729e335f31c44b3b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1f0b12760bd24eae"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2995,7 +2995,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1105a105d9f1406c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf1506f45173541a9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3025,7 +3025,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rea438f874be84daf"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R978b89746738452b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3055,7 +3055,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R98297b63f66f4a97"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1dd3fff251474486"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4337,7 +4337,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R585930cb489a45a4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re52009ec64d54e7c"/>
 </x:worksheet>
 </file>
 
@@ -5341,7 +5341,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf93e3c0e9944c5e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5c48635adbd44e8"/>
 </x:worksheet>
 </file>
 
@@ -12163,7 +12163,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R219cbe2d8f074248"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87acc48160aa4862"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17202,7 +17202,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbeb6791ce11a4eb0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfca7ec39545f4a5b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25181,7 +25181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f36abef9ab44202"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8ea5e72f5f94600"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29120,7 +29120,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d6d65184d69425f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63305df62d664fb8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31184,7 +31184,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27698423ee544fa2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f3c351e1d234cf3"/>
 </x:worksheet>
 </file>
 
